--- a/02-Execucao/03-Execucao_Procedimentos/01-Insumos/mapa-verificacao-achados.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/01-Insumos/mapa-verificacao-achados.xlsx
@@ -373,9 +373,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:D5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -428,12 +430,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ajustes de respostas decorrentes da avaliação de evidências</t>
+          <t>Painel consolidado da avalia??o de evid?ncias</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260621-ajustes-evidencias-para-auditoria.xlsx</t>
+          <t>painel-avaliacao-evidencias.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/02-Execucao/03-Execucao_Procedimentos/01-Insumos/mapa-verificacao-achados.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/01-Insumos/mapa-verificacao-achados.xlsx
@@ -407,11 +407,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A3:D5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1514,7 +1512,7 @@
       <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>institua formalmente Comitê de TIC ou instância equivalente, atentando-se, minimamente, em definir sua composição, competências, periodicidade de reuniões, forma de registro das deliberações e acompanhamento dos encaminhamentos</t>
+          <t>institua formalmente Comitê de TIC ou instância equivalente, compatível com o porte e a estrutura decisória da organização, atentando-se, minimamente, em definir sua composição, competências, periodicidade de reuniões, forma de registro das deliberações e acompanhamento dos encaminhamentos</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1568,7 @@
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, atentando-se, minimamente, em realizar reuniões periódicas, registrar atas, deliberações e encaminhamentos e acompanhar as decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
+          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, compatível com o porte e a estrutura decisória da organização, atentando-se, minimamente, em realizar reuniões periódicas, registrar deliberações e acompanhar decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1624,7 @@
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, atentando-se, minimamente, em realizar reuniões periódicas, registrar atas, deliberações e encaminhamentos e acompanhar as decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
+          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, compatível com o porte e a estrutura decisória da organização, atentando-se, minimamente, em realizar reuniões periódicas, registrar deliberações e acompanhar decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1680,7 @@
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1736,7 @@
       <c r="O18" s="6" t="n"/>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1792,7 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1848,7 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3416,7 @@
       <c r="O48" s="6" t="n"/>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3472,7 @@
       <c r="O49" s="6" t="n"/>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3528,7 @@
       <c r="O50" s="8" t="n"/>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3584,7 @@
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="8" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3640,7 @@
       <c r="O52" s="8" t="n"/>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3696,7 @@
       <c r="O53" s="8" t="n"/>
       <c r="P53" s="8" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3752,7 @@
       <c r="O54" s="8" t="n"/>
       <c r="P54" s="8" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3808,7 @@
       <c r="O55" s="8" t="n"/>
       <c r="P55" s="8" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3864,7 @@
       <c r="O56" s="6" t="n"/>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4965,7 @@
       <c r="O76" s="6" t="n"/>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5021,7 @@
       <c r="O77" s="6" t="n"/>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5077,7 @@
       <c r="O78" s="6" t="n"/>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5133,7 @@
       <c r="O79" s="6" t="n"/>
       <c r="P79" s="6" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5189,7 @@
       <c r="O80" s="6" t="n"/>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5246,7 @@
       <c r="O81" s="6" t="n"/>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>estabeleça a submissão das contratações de TIC à análise prévia e à aprovação técnica da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente, facultando a adoção de fluxos simplificados ou a dispensa de parecer detalhado para contratações diretas por dispensa em razão do valor (baixo valor) ou de baixa complexidade técnica, mediante critérios objetivos ou catálogos de soluções padronizadas</t>
+          <t>estabeleça a submissão das contratações de TIC à análise prévia da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente, admitindo fluxos simplificados para contratações de baixa complexidade ou baixo valor, desde que preservada análise técnica mínima compatível com o risco da contratação</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5816,7 @@
       </c>
       <c r="P92" s="5" t="inlineStr">
         <is>
-          <t>institua formalmente Comitê de TIC ou instância equivalente, atentando-se, minimamente, em definir sua composição, competências, periodicidade de reuniões, forma de registro das deliberações e acompanhamento dos encaminhamentos</t>
+          <t>institua formalmente Comitê de TIC ou instância equivalente, compatível com o porte e a estrutura decisória da organização, atentando-se, minimamente, em definir sua composição, competências, periodicidade de reuniões, forma de registro das deliberações e acompanhamento dos encaminhamentos</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5865,7 @@
       </c>
       <c r="P93" s="5" t="inlineStr">
         <is>
-          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, atentando-se, minimamente, em realizar reuniões periódicas, registrar atas, deliberações e encaminhamentos e acompanhar as decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
+          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, compatível com o porte e a estrutura decisória da organização, atentando-se, minimamente, em realizar reuniões periódicas, registrar deliberações e acompanhar decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5914,7 @@
       </c>
       <c r="P94" s="5" t="inlineStr">
         <is>
-          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, atentando-se, minimamente, em realizar reuniões periódicas, registrar atas, deliberações e encaminhamentos e acompanhar as decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
+          <t>assegure o funcionamento efetivo do Comitê de TIC ou instância equivalente, compatível com o porte e a estrutura decisória da organização, atentando-se, minimamente, em realizar reuniões periódicas, registrar deliberações e acompanhar decisões sobre prioridades, projetos, riscos, serviços, orçamento e contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5963,7 @@
       </c>
       <c r="P95" s="5" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6012,7 @@
       </c>
       <c r="P96" s="5" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6061,7 @@
       </c>
       <c r="P97" s="5" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6110,7 @@
       </c>
       <c r="P98" s="5" t="inlineStr">
         <is>
-          <t>institua processo formal de planejamento de TIC, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
+          <t>institua processo formal de planejamento de TIC, compatível com o porte e a maturidade da organização, atentando-se, minimamente, em definir etapas, responsáveis, participação das áreas demandantes e critérios de priorização das necessidades e iniciativas de TIC</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7363,7 @@
       <c r="O122" s="11" t="n"/>
       <c r="P122" s="10" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7419,7 @@
       <c r="O123" s="11" t="n"/>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7475,7 @@
       <c r="O124" s="11" t="n"/>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7531,7 @@
       <c r="O125" s="11" t="n"/>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7587,7 @@
       <c r="O126" s="11" t="n"/>
       <c r="P126" s="10" t="inlineStr">
         <is>
-          <t>avalie o modelo de operação de TIC e adote medidas para assegurar capacidade interna mínima de coordenação, planejamento, aprovação técnica, fiscalização contratual, tomada de decisão e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
+          <t>avalie o modelo de operação de TIC e adote medidas proporcionais para assegurar capacidade interna suficiente de coordenação, planejamento, aprovação técnica, fiscalização contratual e retenção de conhecimento, especialmente quando a execução das atividades de TIC depender predominantemente de terceiros ou de estrutura externa</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8590,7 @@
       </c>
       <c r="P146" s="5" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8639,7 @@
       </c>
       <c r="P147" s="5" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8688,7 @@
       </c>
       <c r="P148" s="5" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8737,7 @@
       </c>
       <c r="P149" s="5" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8786,7 @@
       </c>
       <c r="P150" s="5" t="inlineStr">
         <is>
-          <t>formalize e padronize o processo de contratação de TIC, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
+          <t>formalize e padronize o processo de contratação de TIC, compatível com o porte, a complexidade e os riscos das contratações da organização, atentando-se, minimamente, em definir fluxo, etapas, papéis, responsabilidades, instâncias de aprovação e modelos de artefatos, manuais, listas de verificação ou orientações internas aplicáveis</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8836,7 @@
       </c>
       <c r="P151" s="5" t="inlineStr">
         <is>
-          <t>estabeleça a submissão das contratações de TIC à análise prévia e à aprovação técnica da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente, facultando a adoção de fluxos simplificados ou a dispensa de parecer detalhado para contratações diretas por dispensa em razão do valor (baixo valor) ou de baixa complexidade técnica, mediante critérios objetivos ou catálogos de soluções padronizadas</t>
+          <t>estabeleça a submissão das contratações de TIC à análise prévia da área de TIC, inclusive quando demandadas por outras áreas, de modo a verificar a compatibilidade da solução com os padrões tecnológicos, os requisitos institucionais, a segurança da informação e a arquitetura existente, admitindo fluxos simplificados para contratações de baixa complexidade ou baixo valor, desde que preservada análise técnica mínima compatível com o risco da contratação</t>
         </is>
       </c>
     </row>

--- a/02-Execucao/03-Execucao_Procedimentos/01-Insumos/mapa-verificacao-achados.xlsx
+++ b/02-Execucao/03-Execucao_Procedimentos/01-Insumos/mapa-verificacao-achados.xlsx
@@ -10,12 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes de Informação" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procedimentos de Auditoria" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ações de Verificação" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variáveis Temporárias" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Motivos do Relatório" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variáveis Temporárias" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Procedimentos de Auditoria'!$A$3:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ações de Verificação'!$A$3:$P$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Variáveis Temporárias'!$A$3:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Motivos do Relatório'!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Variáveis Temporárias'!$A$3:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -24,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -54,8 +56,15 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,14 +82,38 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="6">
@@ -93,7 +126,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -128,6 +161,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5551,7 +5593,7 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que a área de TI possui atribuições formalizadas relacionadas à governança, planejamento ou gestão de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -5600,7 +5642,7 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que define os papéis e responsabilidades da área de gestão de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -5649,7 +5691,7 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -5698,7 +5740,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
@@ -5747,7 +5789,7 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que os indicadores de desempenho da gestão de tecnologia da informação estão implantados (há coleta e análise dos dados necessários à medição de desempenho). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
@@ -5796,7 +5838,7 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -5845,7 +5887,7 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -5894,7 +5936,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o comitê de tecnologia da informação realiza as atividades previstas em ato constitutivo. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
@@ -5943,7 +5985,7 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
@@ -5992,7 +6034,7 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que estabeleceu critérios para orientar a seleção e a priorização das iniciativas de TI (projetos e ações) e os mantêm atualizados. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -6041,7 +6083,7 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -6090,7 +6132,7 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de planejamento de TI está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
@@ -6139,7 +6181,7 @@
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
@@ -6188,7 +6230,7 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as iniciativas de TI (projetos e ações) constantes do plano de TI alinham-se aos objetivos e iniciativas definidos no planejamento institucional (como PPA, planos estratégicos, planos setoriais e plano de governo, no caso de municípios), bem como, quando aplicável, às estratégias e diretrizes estabelecidas por instâncias superiores de governança (como a Estratégia Nacional de Tecnologia da Informação e Comunicação do Poder Judiciário - ENTIC-JUD, normas e orientações do SETIC/PRODERJ (para órgãos estaduais) ou instâncias de governança equivalentes no âmbito municipal). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
@@ -6237,7 +6279,7 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -6286,7 +6328,7 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que na elaboração do PCA são considerados os demais instrumentos de planejamento da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
@@ -6335,7 +6377,7 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o PCA fundamenta a proposta orçamentária da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
@@ -6384,7 +6426,7 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que é feito acompanhamento concomitante à execução do plano de TI, com vistas a assegurar sua observância e possibilitar a realização de ajustes que se fizerem necessário. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
@@ -6436,7 +6478,7 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se o quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação com base em critério(s) ou procedimento(s) técnico(s). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
@@ -6489,7 +6531,7 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se, de maneira documentada, um quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
@@ -6541,7 +6583,7 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos efetivos em tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
@@ -6594,7 +6636,7 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
@@ -6646,7 +6688,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos efetivos em segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
@@ -6699,7 +6741,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
@@ -6748,7 +6790,7 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as responsabilidades e atribuições dos gestores da área de tecnologia da informação estão definidas, documentadas e publicadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
@@ -6800,7 +6842,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que relacionou-se, no perfil profissional, além de requerimentos de ordem legal, um conjunto de competências e habilidades que os ocupantes dos cargos de gestão devem possuir. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
@@ -6853,7 +6895,7 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as responsabilidades e atribuições das ocupações ou grupo de ocupações da área de tecnologia da informação estão definidas, documentadas e publicadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
@@ -6905,7 +6947,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que relacionou-se, no perfil profissional, além de requerimentos de ordem legal, um conjunto de competências e habilidades que os ocupantes dos cargos devem possuir. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I114" s="11" t="n"/>
@@ -6958,7 +7000,7 @@
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
@@ -7010,7 +7052,7 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as lacunas de competências de liderança e gestão necessárias para a atuação dos gestores da organização são identificadas e documentadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I116" s="11" t="n"/>
@@ -7066,7 +7108,7 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as lacunas de competências técnicas da área de tecnologia da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
@@ -7122,7 +7164,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as lacunas de competências técnicas da área de segurança da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
@@ -7175,7 +7217,7 @@
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que elabora plano de capacitação (plano de treinamento) visando o tratamento das lacunas de competência identificadas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -7227,7 +7269,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que incentiva seus colaboradores e gestores a participar das ações de capacitação existentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I120" s="11" t="n"/>
@@ -7283,7 +7325,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que monitora a participação dos colaboradores e gestores nas ações de capacitação existentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I121" s="11" t="n"/>
@@ -7339,7 +7381,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se o quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação com base em critério(s) ou procedimento(s) técnico(s). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
@@ -7395,7 +7437,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu-se, de maneira documentada, um quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I123" s="11" t="n"/>
@@ -7451,7 +7493,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I124" s="11" t="n"/>
@@ -7507,7 +7549,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que são disponibilizados artefatos padronizados para a gestão e fiscalização de contratos de TI, como modelos de plano de fiscalização, termos de recebimento, relatórios de acompanhamento, registros de ocorrências, avaliações de desempenho contratual ou documentos equivalentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I125" s="11" t="n"/>
@@ -7563,7 +7605,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I126" s="11" t="n"/>
@@ -7615,7 +7657,7 @@
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -7663,7 +7705,7 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
@@ -7711,7 +7753,7 @@
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o catálogo é de fácil acesso e está amplamente disponível a seus usuários e às equipes de suporte. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -7759,7 +7801,7 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que são formalizados ANS contendo metas de nível de serviço acordadas com representantes das áreas de negócio clientes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
@@ -7807,7 +7849,7 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
@@ -7855,7 +7897,7 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
@@ -7906,7 +7948,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que mantém um inventário dos ativos associados à informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I133" s="11" t="n"/>
@@ -7961,7 +8003,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu responsabilidades pelos ativos associados à informação. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I134" s="11" t="n"/>
@@ -8013,7 +8055,7 @@
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que gerencia (inventaria e controla) os dispositivos conectados em sua rede. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
@@ -8061,7 +8103,7 @@
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
@@ -8109,7 +8151,7 @@
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
@@ -8160,7 +8202,7 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I138" s="11" t="n"/>
@@ -8212,7 +8254,7 @@
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de gestão de configuração e ativos está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
@@ -8260,7 +8302,7 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu regras para a priorização e o escalamento de incidentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
@@ -8311,7 +8353,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I141" s="11" t="n"/>
@@ -8366,7 +8408,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I142" s="11" t="n"/>
@@ -8418,7 +8460,7 @@
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o(s) processo(s) de gestão de incidentes está(ão) formalizado(s) (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades). Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -8466,7 +8508,7 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
@@ -8517,7 +8559,7 @@
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que definiu procedimentos e responsabilidades quanto à análise dos incidentes, identificação de causas raízes e planejamento e implementação de ações corretivas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="I145" s="11" t="n"/>
@@ -8570,7 +8612,7 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para o planejamento das contratações de TI contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
@@ -8619,7 +8661,7 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para a seleção de fornecedores contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
@@ -8668,7 +8710,7 @@
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que são disponibilizados artefatos padronizados para a fase de seleção de fornecedores, como minutas, checklists, modelos de edital, pareceres, critérios de julgamento ou documentos equivalentes. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
@@ -8717,7 +8759,7 @@
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
@@ -8766,7 +8808,7 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
@@ -8816,7 +8858,7 @@
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
@@ -8864,7 +8906,7 @@
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
@@ -8912,7 +8954,7 @@
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que na elaboração do PCA são considerados os demais instrumentos de planejamento da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
@@ -8960,7 +9002,7 @@
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>Evidência insuficiente para comprovar a prática declarada de que o PCA fundamenta a proposta orçamentária da organização. Justificativa da avaliação: {avaliacao_justificativa}</t>
+          <t>A organização declarou "{resposta_afirmada}" no {item_avaliado}, mas a evidência encaminhada foi considerada insuficiente para comprovar que {pratica}. Justificativa da avaliação: {avaliacao_justificativa}</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
@@ -8993,6 +9035,4295 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:H113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="4" min="1" max="1"/>
+    <col width="18" customWidth="1" style="4" min="2" max="2"/>
+    <col width="65" customWidth="1" style="4" min="3" max="3"/>
+    <col width="10" customWidth="1" style="4" min="4" max="4"/>
+    <col width="22" customWidth="1" style="4" min="5" max="5"/>
+    <col width="24" customWidth="1" style="4" min="6" max="6"/>
+    <col width="110" customWidth="1" style="4" min="7" max="7"/>
+    <col width="10" customWidth="1" style="4" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Identificador do motivo do relatório</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Procedimento de auditoria ao qual o motivo se vincula</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Situação inconforme em que o motivo será exibido</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Ordem de exibição dentro da situação</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Expressão lógica com ações de verificação para exibir o motivo</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Ações de verificação cujas evidências serão referenciadas como E1, E2 etc.</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Texto do motivo a apresentar no relatório; aceita expressões Jinja com dados das ações, ex. {{ AV01.situacao_encontrada }}</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>TRUE/FALSE para ativar ou desativar a regra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>id_procedimento</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>descricao_situacao_inconforme</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>ordem</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>condicao_exibicao</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>acoes_referencia</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>texto_motivo</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>MR001</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de área, unidade, setor ou função de TIC formalmente instituída.</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>AV01</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>AV01</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Item 0101: a organização informou que não há área de TI formalmente instituída no organograma</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>MR002</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Área de TIC sem atribuições formais suficientes para planejamento, coordenação, gestão, execução, monitoramento e controle da TIC.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>AV02 &amp; (AV03 | AV04 | AV84)</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>AV02</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Item 0101: a organização informou possuir área ou modelo de operação de TI, o que levou à análise da suficiência de suas atribuições formais</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>MR003</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Área de TIC sem atribuições formais suficientes para planejamento, coordenação, gestão, execução, monitoramento e controle da TIC.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>AV02 &amp; AV84</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>AV84</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Item 0103: a organização declarou que o setor de TI possui atribuições formalizadas relacionadas à governança, planejamento ou gestão de tecnologia da informação, mas a evidência foi insuficiente para comprovar a prática declarada</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>MR004</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Área de TIC sem atribuições formais suficientes para planejamento, coordenação, gestão, execução, monitoramento e controle da TIC.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>AV02 &amp; AV03</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>AV03</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Item 0103: a organização informou que não há atribuições ou competências da área de TI formalmente definidas</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>MR005</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Área de TIC sem atribuições formais suficientes para planejamento, coordenação, gestão, execução, monitoramento e controle da TIC.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>AV02 &amp; AV04 &amp; ~AV84</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>AV04</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Item 0103: a organização não declarou possuir atribuições formalizadas relacionadas à governança, planejamento ou gestão de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>MR006</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Posicionamento organizacional inadequado da área de TIC.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>AV05 &amp; AV06</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>AV05</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Item 0101: a organização informou possuir área ou modelo de operação de TI, o que levou à análise do seu posicionamento organizacional</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>MR007</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Posicionamento organizacional inadequado da área de TIC.</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>AV05 &amp; AV06</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>AV06</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Item 0102: o posicionamento hierárquico informado pela organização não demonstrou compatibilidade suficiente com a relevância institucional, as responsabilidades e a necessidade de interação da TIC com a alta administração</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>MR008</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>AV07 &amp; ~AV85</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>AV07</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 1001, não houve declaração afirmativa quanto à prática avaliada: define os papéis e responsabilidades da área de gestão de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>MR009</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>AV85</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>AV85</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 1001, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que define os papéis e responsabilidades da área de gestão de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>MR010</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>AV08 &amp; ~AV86</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>AV08</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>No subitem h) do item 1001, não houve declaração afirmativa quanto à prática avaliada: estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>MR011</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>AV86</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>AV86</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>No subitem h) do item 1001, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>MR012</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>AV09 &amp; ~AV87</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>AV09</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 1002, não houve declaração afirmativa quanto à prática avaliada: rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>MR013</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>AV87</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>AV87</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 1002, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>MR014</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>AV10 &amp; ~AV88</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>AV10</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 1002, não houve declaração afirmativa quanto à prática avaliada: os indicadores de desempenho da gestão de tecnologia da informação estão implantados (há coleta e análise dos dados necessários à medição de desempenho)</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>MR015</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>AV88</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>AV88</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 1002, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que os indicadores de desempenho da gestão de tecnologia da informação estão implantados (há coleta e análise dos dados necessários à medição de desempenho)</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>MR016</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente não instituído formalmente.</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>AV11 &amp; ~AV89</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>AV11</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 1001, não houve declaração afirmativa quanto à prática avaliada: dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>MR017</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente não instituído formalmente.</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>AV89</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>AV89</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 1001, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>MR018</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>AV12 &amp; ~AV90 &amp; (AV13 | AV91)</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>AV12</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 1001, a organização declarou dispor de comitê de tecnologia da informação composto por representantes de áreas relevantes, o que levou à análise de sua atuação efetiva</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>MR019</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>AV90 &amp; (AV13 | AV91)</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>AV90</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 1001, a organização declarou dispor de comitê de tecnologia da informação composto por representantes de áreas relevantes, mas a evidência foi insuficiente para comprovar a prática declarada</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>MR020</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>AV13 &amp; ~AV91 &amp; (AV12 | AV90)</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>AV13</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>No subitem f) do item 1001, não houve declaração afirmativa quanto à atuação do comitê de tecnologia da informação nas atividades previstas em ato constitutivo</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>MR021</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>AV91 &amp; (AV12 | AV90)</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>AV91</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>No subitem f) do item 1001, a organização declarou atuação do comitê de tecnologia da informação, mas a evidência foi insuficiente para comprovar a prática declarada</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>MR022</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>AV14 &amp; ~AV92</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>AV14</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2101, não houve declaração afirmativa quanto à prática avaliada: as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>MR023</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>AV92</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>AV92</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2101, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>MR024</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>AV15 &amp; ~AV93</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>AV15</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2101, não houve declaração afirmativa quanto à prática avaliada: estabeleceu critérios para orientar a seleção e a priorização das iniciativas de TI (projetos e ações) e os mantêm atualizados</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>MR025</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>AV93</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>AV93</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2101, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que estabeleceu critérios para orientar a seleção e a priorização das iniciativas de TI (projetos e ações) e os mantêm atualizados</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>MR026</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>AV16 &amp; ~AV94</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>AV16</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2101, não houve declaração afirmativa quanto à prática avaliada: as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações)</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>MR027</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>AV94</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>AV94</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2101, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações)</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>MR028</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>AV17 &amp; ~AV95</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>AV17</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2101, não houve declaração afirmativa quanto à prática avaliada: o processo de planejamento de TI está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>MR029</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>AV95</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>AV95</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2101, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o processo de planejamento de TI está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>MR030</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de aprovação formal do plano de TIC.</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>AV18 &amp; ~AV96</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>AV18</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2102, não houve declaração afirmativa quanto à prática avaliada: o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>MR031</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de aprovação formal do plano de TIC.</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>AV96</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>AV96</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2102, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>MR032</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem alinhamento adequado ao planejamento institucional.</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>AV19 &amp; ~AV97</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>AV19</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2102, não houve declaração afirmativa quanto à prática avaliada: as iniciativas de TI (projetos e ações) constantes do plano de TI alinham-se aos objetivos e iniciativas definidos no planejamento institucional (como PPA, planos estratégicos, planos setoriais e plano de governo, no caso de municípios), bem como, quando aplicável, às estratégias e diretrizes estabelecidas por instâncias superiores de governança (como a Estratégia Nacional de Tecnologia da Informação e Comunicação do Poder Judiciário - ENTIC-JUD, normas e orientações do SETIC/PRODERJ (para órgãos estaduais) ou instâncias de governança equivalentes no âmbito municipal)</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>MR033</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem alinhamento adequado ao planejamento institucional.</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>AV97</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>AV97</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2102, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que as iniciativas de TI (projetos e ações) constantes do plano de TI alinham-se aos objetivos e iniciativas definidos no planejamento institucional (como PPA, planos estratégicos, planos setoriais e plano de governo, no caso de municípios), bem como, quando aplicável, às estratégias e diretrizes estabelecidas por instâncias superiores de governança (como a Estratégia Nacional de Tecnologia da Informação e Comunicação do Poder Judiciário - ENTIC-JUD, normas e orientações do SETIC/PRODERJ (para órgãos estaduais) ou instâncias de governança equivalentes no âmbito municipal)</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>MR034</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>AV20 &amp; ~AV98</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>AV20</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2102, não houve declaração afirmativa quanto à prática avaliada: o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>MR035</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>AV98</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>AV98</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2102, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>MR036</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>AV21 &amp; ~AV99</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>AV21</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2802, não houve declaração afirmativa quanto à prática avaliada: na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>MR037</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>AV99</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>AV99</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2802, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>MR038</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>AV22 &amp; ~AV100</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>AV22</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2802, não houve declaração afirmativa quanto à prática avaliada: o PCA fundamenta a proposta orçamentária da organização</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>MR039</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>AV100</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>AV100</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2802, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o PCA fundamenta a proposta orçamentária da organização</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>MR040</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>AV23</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>AV23</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2804, não houve declaração afirmativa quanto à prática avaliada: as contratações de TI executadas no exercício encontram-se previamente estabelecidas nos instrumentos de planejamento vigentes (PDTI/PEDTIC e PCA)</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>MR041</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de acompanhamento, revisão ou atualização periódica do plano de TIC.</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>AV24 &amp; ~AV101</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>AV24</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2102, não houve declaração afirmativa quanto à prática avaliada: é feito acompanhamento concomitante à execução do plano de TI, com vistas a assegurar sua observância e possibilitar a realização de ajustes que se fizerem necessário</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>MR042</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de acompanhamento, revisão ou atualização periódica do plano de TIC.</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>AV101</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>AV101</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2102, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que é feito acompanhamento concomitante à execução do plano de TI, com vistas a assegurar sua observância e possibilitar a realização de ajustes que se fizerem necessário</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>MR043</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de força de trabalho dedicada à TIC ou à segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>AV25</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>AV25</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>Não foi identificada força de trabalho dedicada à TIC no quantitativo informado pela organização</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>MR044</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de força de trabalho dedicada à TIC ou à segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>AV27</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>AV27</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>Não foi identificada força de trabalho dedicada à segurança da informação no quantitativo informado pela organização</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>MR045</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>AV29 &amp; ~AV103</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>AV29</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2703, não houve declaração afirmativa quanto à prática avaliada: definiu-se, de maneira documentada, um quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>MR046</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>AV103</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>AV103</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2703, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que definiu-se, de maneira documentada, um quantitativo necessário de pessoal da área de tecnologia da informação e segurança da informação</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>MR047</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>AV31 &amp; ~AV105</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>AV31</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2708, não houve declaração afirmativa quanto à prática avaliada: possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>MR048</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>AV105</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>AV105</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2708, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>MR049</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>AV33 &amp; ~AV107</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>AV33</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2708, não houve declaração afirmativa quanto à prática avaliada: possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>MR050</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>AV107</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>AV107</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2708, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>MR051</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>AV34 &amp; ~AV108</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>AV34</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2701, não houve declaração afirmativa quanto à prática avaliada: as responsabilidades e atribuições dos gestores da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>MR052</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>AV108</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>AV108</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2701, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que as responsabilidades e atribuições dos gestores da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>MR053</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>AV36 &amp; ~AV110</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>AV36</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2702, não houve declaração afirmativa quanto à prática avaliada: as responsabilidades e atribuições das ocupações ou grupo de ocupações da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>MR054</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>AV110</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>AV110</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2702, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que as responsabilidades e atribuições das ocupações ou grupo de ocupações da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>MR055</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>AV38 &amp; ~AV112</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>AV38</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2704, não houve declaração afirmativa quanto à prática avaliada: os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>MR056</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>AV112</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>AV112</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2704, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>MR057</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>AV39</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>AV39</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2705, não houve declaração afirmativa quanto à prática avaliada: as lacunas de competências de liderança e gestão necessárias para a atuação dos gestores da organização são identificadas e documentadas</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>MR058</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>AV40</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>AV40</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2705, não houve declaração afirmativa quanto à prática avaliada: as lacunas de competências técnicas da área de tecnologia da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>MR059</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>AV41</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>AV41</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2705, não houve declaração afirmativa quanto à prática avaliada: as lacunas de competências técnicas da área de segurança da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>MR060</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>AV42 &amp; ~AV116</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>AV42</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2706, não houve declaração afirmativa quanto à prática avaliada: elabora plano de capacitação (plano de treinamento) visando o tratamento das lacunas de competência identificadas</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>MR061</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>AV116</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>AV116</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2706, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que elabora plano de capacitação (plano de treinamento) visando o tratamento das lacunas de competência identificadas</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>MR062</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Dependência externa relevante sem capacidade interna suficiente para coordenar e fiscalizar a TIC.</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>AV45 &amp; AV46</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>AV45</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>A organização informou modelo de operação de TIC com execução predominantemente terceirizada ou prestada por estrutura central externa, o que levou à análise de sua capacidade interna de coordenação e fiscalização</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>MR063</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>Dependência externa relevante sem capacidade interna suficiente para coordenar e fiscalizar a TIC.</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>AV45 &amp; AV46</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>AV46</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>Não foi identificado quantitativo de profissionais internos de TIC suficiente para coordenar e fiscalizar a execução das atividades de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>MR064</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Dependência externa relevante sem capacidade interna suficiente para coordenar e fiscalizar a TIC.</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>AV53</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>AV53</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>O quantitativo informado indicou predominância de profissionais terceirizados em relação aos profissionais internos de TIC</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>MR065</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>AV54 &amp; ~AV124</t>
+        </is>
+      </c>
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>AV54</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2201, não houve declaração afirmativa quanto à prática avaliada: o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes)</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>MR066</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>AV124</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>AV124</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2201, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes)</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>MR067</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>AV55 &amp; ~AV125</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>AV55</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2201, não houve declaração afirmativa quanto à prática avaliada: o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>MR068</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>AV125</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>AV125</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2201, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>MR069</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>AV56 &amp; ~AV126</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>AV56</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2201, não houve declaração afirmativa quanto à prática avaliada: o catálogo é de fácil acesso e está amplamente disponível a seus usuários e às equipes de suporte</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>MR070</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>AV126</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>AV126</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2201, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o catálogo é de fácil acesso e está amplamente disponível a seus usuários e às equipes de suporte</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>MR071</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade na definição e no monitoramento de níveis mínimos de serviço de TIC.</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>AV57 &amp; ~AV127</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>AV57</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2201, não houve declaração afirmativa quanto à prática avaliada: são formalizados ANS contendo metas de nível de serviço acordadas com representantes das áreas de negócio clientes</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>MR072</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade na definição e no monitoramento de níveis mínimos de serviço de TIC.</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>AV127</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>AV127</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2201, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que são formalizados ANS contendo metas de nível de serviço acordadas com representantes das áreas de negócio clientes</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>MR073</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade na definição e no monitoramento de níveis mínimos de serviço de TIC.</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>AV58 &amp; ~AV128</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>AV58</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2201, não houve declaração afirmativa quanto à prática avaliada: a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>MR074</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade na definição e no monitoramento de níveis mínimos de serviço de TIC.</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>AV128</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>AV128</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2201, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>MR075</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>AV59 &amp; ~AV129</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>AV59</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2203, não houve declaração afirmativa quanto à prática avaliada: mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>MR076</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>AV129</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>AV129</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2203, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>MR077</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>AV62 &amp; ~AV132</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>AV62</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2504, não houve declaração afirmativa quanto à prática avaliada: gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>MR078</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>AV132</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>AV132</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2504, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>MR079</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>AV63 &amp; ~AV133</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>AV63</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2504, não houve declaração afirmativa quanto à prática avaliada: gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>MR080</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>AV133</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>AV133</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2504, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>MR081</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>AV64 &amp; ~AV134</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>AV64</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2203, não houve declaração afirmativa quanto à prática avaliada: mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>MR082</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>AV134</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>AV134</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2203, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>MR083</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>AV66 &amp; ~AV136</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>AV66</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2203, não houve declaração afirmativa quanto à prática avaliada: o processo de gestão de configuração e ativos está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>MR084</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>Ausência ou fragilidade do processo de gestão de configuração.</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>AV136</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>AV136</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2203, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o processo de gestão de configuração e ativos está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>MR085</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>AV67 &amp; ~AV137</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>AV67</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2204, não houve declaração afirmativa quanto à prática avaliada: definiu regras para a priorização e o escalamento de incidentes</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>MR086</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>AV137</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>AV137</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2204, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que definiu regras para a priorização e o escalamento de incidentes</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>MR087</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>AV70 &amp; ~AV140</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>AV70</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2204, não houve declaração afirmativa quanto à prática avaliada: o(s) processo(s) de gestão de incidentes está(ão) formalizado(s) (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>MR088</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>AV140</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>AV140</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2204, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o(s) processo(s) de gestão de incidentes está(ão) formalizado(s) (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>MR089</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>AV71 &amp; ~AV141</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>AV71</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2204, não houve declaração afirmativa quanto à prática avaliada: definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>MR090</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>AV141</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>AV141</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2204, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>MR091</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>AV73 &amp; ~AV143</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>AV73</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2801, não houve declaração afirmativa quanto à prática avaliada: o processo de trabalho para o planejamento das contratações de TI contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>MR092</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>AV143</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>AV143</t>
+        </is>
+      </c>
+      <c r="G95" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2801, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o processo de trabalho para o planejamento das contratações de TI contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>MR093</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>AV74 &amp; ~AV144</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>AV74</t>
+        </is>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2801, não houve declaração afirmativa quanto à prática avaliada: o processo de trabalho para a seleção de fornecedores contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>MR094</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>AV144</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>AV144</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2801, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o processo de trabalho para a seleção de fornecedores contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>MR095</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>AV75 &amp; ~AV145</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>AV75</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2801, não houve declaração afirmativa quanto à prática avaliada: são disponibilizados artefatos padronizados para a fase de seleção de fornecedores, como minutas, checklists, modelos de edital, pareceres, critérios de julgamento ou documentos equivalentes</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>MR096</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>AV145</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>AV145</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2801, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que são disponibilizados artefatos padronizados para a fase de seleção de fornecedores, como minutas, checklists, modelos de edital, pareceres, critérios de julgamento ou documentos equivalentes</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>MR097</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>AV76 &amp; ~AV146</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>AV76</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2801, não houve declaração afirmativa quanto à prática avaliada: o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>MR098</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>No subitem e) do item 2801, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>MR099</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>AV77 &amp; ~AV147</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>AV77</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>No subitem g) do item 2801, não houve declaração afirmativa quanto à prática avaliada: os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>MR100</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="F103" s="15" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>No subitem g) do item 2801, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>MR101</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem análise prévia e aprovação técnica obrigatória da área de TIC.</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>AV78 &amp; ~AV148</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>AV78</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2804, não houve declaração afirmativa quanto à prática avaliada: as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>MR102</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem análise prévia e aprovação técnica obrigatória da área de TIC.</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>AV148</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="inlineStr">
+        <is>
+          <t>AV148</t>
+        </is>
+      </c>
+      <c r="G105" s="15" t="inlineStr">
+        <is>
+          <t>No subitem a) do item 2804, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>MR103</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>AV79 &amp; ~AV149</t>
+        </is>
+      </c>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>AV79</t>
+        </is>
+      </c>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2102, não houve declaração afirmativa quanto à prática avaliada: o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações</t>
+        </is>
+      </c>
+      <c r="H106" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>MR104</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="G107" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2102, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>MR105</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>AV80 &amp; ~AV150</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>AV80</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2802, não houve declaração afirmativa quanto à prática avaliada: na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>MR106</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>AV150</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>AV150</t>
+        </is>
+      </c>
+      <c r="G109" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2802, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>MR107</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>AV81 &amp; ~AV151</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>AV81</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2802, não houve declaração afirmativa quanto à prática avaliada: o PCA fundamenta a proposta orçamentária da organização</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>MR108</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>AV151</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>AV151</t>
+        </is>
+      </c>
+      <c r="G111" s="15" t="inlineStr">
+        <is>
+          <t>No subitem d) do item 2802, a organização declarou a prática avaliada, mas a evidência foi insuficiente para comprovar que o PCA fundamenta a proposta orçamentária da organização</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>MR109</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>AV82</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>AV82</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="inlineStr">
+        <is>
+          <t>No subitem b) do item 2804, não houve declaração afirmativa quanto à prática avaliada: as contratações de TI executadas no exercício encontram-se previamente estabelecidas nos instrumentos de planejamento vigentes (PDTI/PEDTIC e PCA)</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>MR110</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem equipe de planejamento formalmente designada e com participação técnica de TIC.</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>AV83</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>AV83</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="inlineStr">
+        <is>
+          <t>No subitem c) do item 2804, não houve declaração afirmativa quanto à prática avaliada: a fase de planejamento de cada contratação de TI é conduzida por uma Equipe de Planejamento da Contratação formalmente designada (composta, minimamente, por integrante requisitante e integrante técnico da área de TI)</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
